--- a/backend/app/resources/typologies/CCC.xlsx
+++ b/backend/app/resources/typologies/CCC.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sagourram\Desktop\Tawazoon-V3\backend\app\resources\typologies\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C539931-DD34-4AB3-A0FE-6B91EB0AE2EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53BD9977-AAEB-480B-8170-AD5D6F293156}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$232</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
     <author>Mohammed Amine JALAL</author>
   </authors>
   <commentList>
-    <comment ref="G140" authorId="0" shapeId="0" xr:uid="{7046E643-3D84-4065-A44F-44794901FFA9}">
+    <comment ref="G140" authorId="0" shapeId="0" xr:uid="{EEC51897-EF5F-46B4-99F4-A1AF7683C72E}">
       <text>
         <r>
           <rPr>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1278" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1276" uniqueCount="218">
   <si>
     <t>Nom de tâche</t>
   </si>
@@ -310,9 +310,6 @@
     <t>Retour info facteur</t>
   </si>
   <si>
-    <t>Etat argent CRBT</t>
-  </si>
-  <si>
     <t>Mise en sac</t>
   </si>
   <si>
@@ -541,9 +538,6 @@
     <t>CO Arrivé Axes</t>
   </si>
   <si>
-    <t>Chrono forfait</t>
-  </si>
-  <si>
     <t xml:space="preserve"> AMANA Reçu Axes</t>
   </si>
   <si>
@@ -709,25 +703,36 @@
     <t>CONTRÔLEUR OPÉRATIONS</t>
   </si>
   <si>
-    <t>CONTRÔLEUR DE ZONE</t>
-  </si>
-  <si>
     <t>sac</t>
   </si>
   <si>
-    <t>min_retour</t>
-  </si>
-  <si>
     <t>Réception CR avisé sur  SI COM</t>
+  </si>
+  <si>
+    <t>Amana Reçu Axes</t>
+  </si>
+  <si>
+    <t>Amana</t>
+  </si>
+  <si>
+    <t>Etat argent CRBT(Facteur)</t>
+  </si>
+  <si>
+    <t>min_retour_crbt</t>
+  </si>
+  <si>
+    <t>Etat argent CRBT(Guichetier)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="_-* #,##0.0000000_-;\-* #,##0.0000000_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="166" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="11" x14ac:knownFonts="1">
     <font>
@@ -807,7 +812,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -886,6 +891,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="5">
     <border>
@@ -953,7 +964,7 @@
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1083,6 +1094,36 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="14" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="4" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="14" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="14" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1437,7 +1478,7 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B2" s="9" t="s">
         <v>10</v>
@@ -1447,16 +1488,16 @@
       </c>
       <c r="D2" s="54"/>
       <c r="E2" s="14" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F2" s="19">
         <v>1</v>
       </c>
       <c r="G2" s="32" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H2" s="14" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="I2" s="33">
         <v>7.3499999999999996E-2</v>
@@ -1467,7 +1508,7 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B3" s="10" t="s">
         <v>12</v>
@@ -1477,16 +1518,16 @@
       </c>
       <c r="D3" s="54"/>
       <c r="E3" s="14" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F3" s="20">
         <v>1</v>
       </c>
       <c r="G3" s="32" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H3" s="14" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="I3" s="33">
         <v>6.0499999999999998E-2</v>
@@ -1497,7 +1538,7 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B4" s="9" t="s">
         <v>13</v>
@@ -1507,17 +1548,15 @@
       </c>
       <c r="D4" s="54"/>
       <c r="E4" s="14" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F4" s="21">
         <v>0.4</v>
       </c>
       <c r="G4" s="32" t="s">
-        <v>184</v>
-      </c>
-      <c r="H4" s="14" t="s">
-        <v>209</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="H4" s="54"/>
       <c r="I4" s="33">
         <v>7.2333333333333333E-2</v>
       </c>
@@ -1527,7 +1566,7 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B5" s="9" t="s">
         <v>13</v>
@@ -1536,16 +1575,16 @@
         <v>11</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F5" s="21">
         <v>0.6</v>
       </c>
       <c r="G5" s="32" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H5" s="14" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="I5" s="33">
         <v>7.2333333333333333E-2</v>
@@ -1559,18 +1598,18 @@
         <v>14</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C6" s="14" t="s">
         <v>15</v>
       </c>
       <c r="D6" s="55"/>
       <c r="E6" s="14" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="F6" s="22"/>
       <c r="G6" s="9" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H6" s="14"/>
       <c r="I6" s="33">
@@ -1588,11 +1627,11 @@
         <v>17</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D7" s="56"/>
       <c r="E7" s="9" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="F7" s="19">
         <v>1</v>
@@ -1616,11 +1655,11 @@
         <v>20</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D8" s="54"/>
       <c r="E8" s="9" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F8" s="20">
         <v>1</v>
@@ -1648,16 +1687,16 @@
       </c>
       <c r="D9" s="54"/>
       <c r="E9" s="14" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F9" s="23">
         <v>1</v>
       </c>
       <c r="G9" s="32" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H9" s="14" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="I9" s="33">
         <v>7.3499999999999996E-2</v>
@@ -1678,16 +1717,16 @@
       </c>
       <c r="D10" s="54"/>
       <c r="E10" s="14" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F10" s="20">
         <v>0.4</v>
       </c>
       <c r="G10" s="32" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H10" s="14" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="I10" s="33">
         <v>6.3166666666666663E-2</v>
@@ -1708,16 +1747,16 @@
       </c>
       <c r="D11" s="57"/>
       <c r="E11" s="14" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F11" s="23">
         <v>0.6</v>
       </c>
       <c r="G11" s="32" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H11" s="14" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="I11" s="33">
         <v>6.3166666666666663E-2</v>
@@ -1728,7 +1767,7 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B12" s="10" t="s">
         <v>12</v>
@@ -1738,16 +1777,16 @@
       </c>
       <c r="D12" s="54"/>
       <c r="E12" s="14" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F12" s="20">
         <v>1</v>
       </c>
       <c r="G12" s="14" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H12" s="14" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="I12" s="33">
         <v>0.16666666666666666</v>
@@ -1764,11 +1803,11 @@
         <v>17</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D13" s="57"/>
       <c r="E13" s="9" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="F13" s="23">
         <v>1</v>
@@ -1792,11 +1831,11 @@
         <v>20</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D14" s="57"/>
       <c r="E14" s="9" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F14" s="19">
         <v>1</v>
@@ -1813,8 +1852,8 @@
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
-        <v>111</v>
+      <c r="A15" s="61" t="s">
+        <v>110</v>
       </c>
       <c r="B15" s="11" t="s">
         <v>10</v>
@@ -1824,15 +1863,15 @@
       </c>
       <c r="D15" s="54"/>
       <c r="E15" s="15" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F15" s="24">
         <v>1</v>
       </c>
-      <c r="G15" s="15" t="s">
-        <v>186</v>
-      </c>
-      <c r="H15" s="15"/>
+      <c r="G15" s="14" t="s">
+        <v>184</v>
+      </c>
+      <c r="H15" s="14"/>
       <c r="I15" s="35">
         <v>7.0833333333333331E-2</v>
       </c>
@@ -1845,18 +1884,18 @@
         <v>25</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C16" s="14" t="s">
         <v>15</v>
       </c>
       <c r="D16" s="55"/>
       <c r="E16" s="14" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="F16" s="25"/>
       <c r="G16" s="9" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H16" s="14"/>
       <c r="I16" s="33">
@@ -1874,11 +1913,11 @@
         <v>17</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D17" s="54"/>
       <c r="E17" s="9" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="F17" s="20">
         <v>1</v>
@@ -1902,11 +1941,11 @@
         <v>20</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D18" s="54"/>
       <c r="E18" s="9" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F18" s="23">
         <v>1</v>
@@ -1923,8 +1962,8 @@
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A19" s="2" t="s">
-        <v>111</v>
+      <c r="A19" s="61" t="s">
+        <v>110</v>
       </c>
       <c r="B19" s="11" t="s">
         <v>13</v>
@@ -1934,16 +1973,16 @@
       </c>
       <c r="D19" s="54"/>
       <c r="E19" s="15" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F19" s="24">
         <v>1</v>
       </c>
-      <c r="G19" s="11" t="s">
-        <v>186</v>
+      <c r="G19" s="32" t="s">
+        <v>184</v>
       </c>
       <c r="H19" s="14" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="I19" s="35">
         <v>0.128</v>
@@ -1953,8 +1992,8 @@
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A20" s="2" t="s">
-        <v>112</v>
+      <c r="A20" s="61" t="s">
+        <v>111</v>
       </c>
       <c r="B20" s="12" t="s">
         <v>12</v>
@@ -1964,15 +2003,15 @@
       </c>
       <c r="D20" s="54"/>
       <c r="E20" s="15" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F20" s="26">
         <v>1</v>
       </c>
-      <c r="G20" s="15" t="s">
-        <v>185</v>
-      </c>
-      <c r="H20" s="15"/>
+      <c r="G20" s="14" t="s">
+        <v>183</v>
+      </c>
+      <c r="H20" s="14"/>
       <c r="I20" s="35">
         <v>0.128</v>
       </c>
@@ -1992,13 +2031,13 @@
       </c>
       <c r="D21" s="55"/>
       <c r="E21" s="14" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F21" s="23">
         <v>1</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="H21" s="14"/>
       <c r="I21" s="33">
@@ -2013,18 +2052,18 @@
         <v>30</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C22" s="14" t="s">
         <v>15</v>
       </c>
       <c r="D22" s="55"/>
       <c r="E22" s="14" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="F22" s="9"/>
       <c r="G22" s="9" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="H22" s="14"/>
       <c r="I22" s="33">
@@ -2042,11 +2081,11 @@
         <v>17</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D23" s="55"/>
       <c r="E23" s="9" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="F23" s="20">
         <v>1</v>
@@ -2070,11 +2109,11 @@
         <v>20</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D24" s="54"/>
       <c r="E24" s="9" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F24" s="23">
         <v>1</v>
@@ -2092,7 +2131,7 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B25" s="10" t="s">
         <v>12</v>
@@ -2102,13 +2141,13 @@
       </c>
       <c r="D25" s="55"/>
       <c r="E25" s="14" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F25" s="21">
         <v>1</v>
       </c>
       <c r="G25" s="14" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="H25" s="14"/>
       <c r="I25" s="33">
@@ -2120,7 +2159,7 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B26" s="9" t="s">
         <v>10</v>
@@ -2130,13 +2169,13 @@
       </c>
       <c r="D26" s="55"/>
       <c r="E26" s="18" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F26" s="19">
         <v>1</v>
       </c>
       <c r="G26" s="32" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H26" s="14"/>
       <c r="I26" s="33">
@@ -2148,23 +2187,23 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C27" s="14" t="s">
         <v>28</v>
       </c>
       <c r="D27" s="55"/>
       <c r="E27" s="14" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F27" s="20">
         <v>1</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="H27" s="14"/>
       <c r="I27" s="33">
@@ -2179,18 +2218,18 @@
         <v>33</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C28" s="14" t="s">
         <v>15</v>
       </c>
       <c r="D28" s="54"/>
       <c r="E28" s="14" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="F28" s="9"/>
       <c r="G28" s="9" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="H28" s="14"/>
       <c r="I28" s="33">
@@ -2208,11 +2247,11 @@
         <v>17</v>
       </c>
       <c r="C29" s="14" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D29" s="54"/>
       <c r="E29" s="9" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="F29" s="20">
         <v>1</v>
@@ -2236,11 +2275,11 @@
         <v>20</v>
       </c>
       <c r="C30" s="14" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D30" s="54"/>
       <c r="E30" s="9" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F30" s="20">
         <v>1</v>
@@ -2268,13 +2307,13 @@
       </c>
       <c r="D31" s="54"/>
       <c r="E31" s="14" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F31" s="23">
         <v>1</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="H31" s="14"/>
       <c r="I31" s="33">
@@ -2296,13 +2335,13 @@
       </c>
       <c r="D32" s="55"/>
       <c r="E32" s="14" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F32" s="19">
         <v>1</v>
       </c>
       <c r="G32" s="14" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="H32" s="14"/>
       <c r="I32" s="33">
@@ -2314,7 +2353,7 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B33" s="10" t="s">
         <v>12</v>
@@ -2324,13 +2363,13 @@
       </c>
       <c r="D33" s="54"/>
       <c r="E33" s="18" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F33" s="21">
         <v>1</v>
       </c>
       <c r="G33" s="14" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="H33" s="14"/>
       <c r="I33" s="33">
@@ -2342,7 +2381,7 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B34" s="9" t="s">
         <v>13</v>
@@ -2352,13 +2391,13 @@
       </c>
       <c r="D34" s="54"/>
       <c r="E34" s="14" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F34" s="23">
         <v>1</v>
       </c>
       <c r="G34" s="9" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="H34" s="14"/>
       <c r="I34" s="33">
@@ -2373,18 +2412,18 @@
         <v>36</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C35" s="14" t="s">
         <v>15</v>
       </c>
       <c r="D35" s="54"/>
       <c r="E35" s="14" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="F35" s="9"/>
       <c r="G35" s="9" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="H35" s="14"/>
       <c r="I35" s="33">
@@ -2402,11 +2441,11 @@
         <v>17</v>
       </c>
       <c r="C36" s="14" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D36" s="54"/>
       <c r="E36" s="9" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="F36" s="20">
         <v>1</v>
@@ -2424,23 +2463,23 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="B37" s="9" t="s">
-        <v>157</v>
+        <v>115</v>
+      </c>
+      <c r="B37" s="62" t="s">
+        <v>177</v>
       </c>
       <c r="C37" s="14" t="s">
         <v>28</v>
       </c>
       <c r="D37" s="54"/>
       <c r="E37" s="14" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F37" s="23">
         <v>1</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="H37" s="14"/>
       <c r="I37" s="33">
@@ -2455,18 +2494,18 @@
         <v>38</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C38" s="14" t="s">
         <v>15</v>
       </c>
       <c r="D38" s="54"/>
       <c r="E38" s="14" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="F38" s="9"/>
       <c r="G38" s="9" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="H38" s="14"/>
       <c r="I38" s="33">
@@ -2480,17 +2519,17 @@
       <c r="A39" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B39" s="10" t="s">
+      <c r="B39" s="9" t="s">
         <v>20</v>
       </c>
       <c r="C39" s="14" t="s">
         <v>18</v>
       </c>
       <c r="D39" s="54" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F39" s="20">
         <v>1</v>
@@ -2508,23 +2547,23 @@
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C40" s="14" t="s">
         <v>28</v>
       </c>
       <c r="D40" s="54"/>
       <c r="E40" s="14" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F40" s="23">
         <v>0.6</v>
       </c>
       <c r="G40" s="9" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="H40" s="14"/>
       <c r="I40" s="33">
@@ -2536,23 +2575,23 @@
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>158</v>
+        <v>213</v>
       </c>
       <c r="C41" s="14" t="s">
         <v>28</v>
       </c>
       <c r="D41" s="54"/>
       <c r="E41" s="14" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F41" s="21">
         <v>0.4</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="H41" s="14"/>
       <c r="I41" s="33">
@@ -2564,51 +2603,51 @@
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="B42" s="9" t="s">
-        <v>157</v>
+        <v>116</v>
+      </c>
+      <c r="B42" s="62" t="s">
+        <v>177</v>
       </c>
       <c r="C42" s="14" t="s">
         <v>28</v>
       </c>
       <c r="D42" s="54"/>
       <c r="E42" s="14" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F42" s="19">
         <v>1</v>
       </c>
       <c r="G42" s="9" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="H42" s="14"/>
       <c r="I42" s="33">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J42" s="43">
-        <v>120</v>
+        <v>30</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="B43" s="10" t="s">
-        <v>159</v>
+        <v>114</v>
+      </c>
+      <c r="B43" s="62" t="s">
+        <v>12</v>
       </c>
       <c r="C43" s="14" t="s">
         <v>28</v>
       </c>
       <c r="D43" s="54"/>
       <c r="E43" s="14" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F43" s="19">
         <v>1</v>
       </c>
       <c r="G43" s="14" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="H43" s="14"/>
       <c r="I43" s="33">
@@ -2620,26 +2659,26 @@
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C44" s="14" t="s">
         <v>28</v>
       </c>
       <c r="D44" s="54"/>
       <c r="E44" s="14" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F44" s="23">
         <v>1</v>
       </c>
       <c r="G44" s="18" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H44" s="14" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="I44" s="33">
         <v>0.1065</v>
@@ -2652,17 +2691,17 @@
       <c r="A45" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B45" s="9" t="s">
+      <c r="B45" s="62" t="s">
         <v>17</v>
       </c>
       <c r="C45" s="14" t="s">
         <v>18</v>
       </c>
       <c r="D45" s="54" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="F45" s="23">
         <v>1</v>
@@ -2683,18 +2722,18 @@
         <v>41</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C46" s="14" t="s">
         <v>15</v>
       </c>
       <c r="D46" s="54"/>
       <c r="E46" s="14" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="F46" s="9"/>
       <c r="G46" s="9" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H46" s="14"/>
       <c r="I46" s="33">
@@ -2716,7 +2755,7 @@
       </c>
       <c r="D47" s="54"/>
       <c r="E47" s="9" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F47" s="20">
         <v>1</v>
@@ -2726,7 +2765,7 @@
       </c>
       <c r="H47" s="14"/>
       <c r="I47" s="33">
-        <v>0.03</v>
+        <v>3.3333333333333333E-2</v>
       </c>
       <c r="J47" s="34">
         <v>2</v>
@@ -2734,23 +2773,23 @@
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>157</v>
+        <v>178</v>
       </c>
       <c r="C48" s="14" t="s">
         <v>28</v>
       </c>
       <c r="D48" s="55"/>
       <c r="E48" s="14" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F48" s="23">
         <v>1</v>
       </c>
-      <c r="G48" s="9" t="s">
-        <v>209</v>
+      <c r="G48" s="14" t="s">
+        <v>183</v>
       </c>
       <c r="H48" s="14"/>
       <c r="I48" s="33">
@@ -2762,23 +2801,23 @@
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>157</v>
+        <v>214</v>
       </c>
       <c r="C49" s="14" t="s">
         <v>28</v>
       </c>
       <c r="D49" s="54"/>
       <c r="E49" s="14" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F49" s="20">
         <v>1</v>
       </c>
-      <c r="G49" s="14" t="s">
-        <v>185</v>
+      <c r="G49" s="9" t="s">
+        <v>207</v>
       </c>
       <c r="H49" s="14"/>
       <c r="I49" s="33">
@@ -2790,30 +2829,30 @@
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>157</v>
+        <v>178</v>
       </c>
       <c r="C50" s="14" t="s">
         <v>28</v>
       </c>
       <c r="D50" s="54"/>
       <c r="E50" s="14" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F50" s="19">
         <v>1</v>
       </c>
       <c r="G50" s="14" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="H50" s="14"/>
       <c r="I50" s="33">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J50" s="45">
-        <v>120</v>
+        <v>30</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.3">
@@ -2821,14 +2860,14 @@
         <v>43</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C51" s="14" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D51" s="54"/>
       <c r="E51" s="14" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F51" s="23">
         <v>1</v>
@@ -2846,19 +2885,19 @@
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C52" s="14" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D52" s="57" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E52" s="14" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F52" s="23">
         <v>1</v>
@@ -2876,19 +2915,19 @@
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C53" s="14" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D53" s="54" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E53" s="14" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F53" s="23">
         <v>1</v>
@@ -2916,7 +2955,7 @@
       </c>
       <c r="D54" s="54"/>
       <c r="E54" s="9" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="F54" s="23">
         <v>1</v>
@@ -2926,7 +2965,7 @@
       </c>
       <c r="H54" s="14"/>
       <c r="I54" s="33">
-        <v>0.03</v>
+        <v>3.3333333333333333E-2</v>
       </c>
       <c r="J54" s="34">
         <v>2</v>
@@ -2937,20 +2976,20 @@
         <v>45</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C55" s="14" t="s">
         <v>15</v>
       </c>
       <c r="D55" s="54"/>
       <c r="E55" s="14" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="F55" s="23">
         <v>1</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="H55" s="14"/>
       <c r="I55" s="33">
@@ -2962,54 +3001,54 @@
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>157</v>
+        <v>214</v>
       </c>
       <c r="C56" s="14" t="s">
         <v>28</v>
       </c>
       <c r="D56" s="54"/>
       <c r="E56" s="14" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F56" s="23">
         <v>1</v>
       </c>
       <c r="G56" s="9" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="H56" s="14"/>
       <c r="I56" s="33">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J56" s="34">
-        <v>120</v>
+        <v>30</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B57" s="10" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C57" s="14" t="s">
         <v>28</v>
       </c>
       <c r="D57" s="54"/>
       <c r="E57" s="14" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F57" s="23">
         <v>1</v>
       </c>
       <c r="G57" s="18" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H57" s="14" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="I57" s="33">
         <v>0.1065</v>
@@ -3020,26 +3059,26 @@
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C58" s="14" t="s">
         <v>28</v>
       </c>
       <c r="D58" s="54"/>
       <c r="E58" s="14" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F58" s="23">
         <v>1</v>
       </c>
       <c r="G58" s="18" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H58" s="14" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="I58" s="33">
         <v>0.1065</v>
@@ -3050,19 +3089,19 @@
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B59" s="9" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C59" s="14" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D59" s="57" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E59" s="14" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F59" s="23">
         <v>1</v>
@@ -3083,20 +3122,20 @@
         <v>47</v>
       </c>
       <c r="B60" s="9" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C60" s="14" t="s">
         <v>15</v>
       </c>
       <c r="D60" s="54"/>
       <c r="E60" s="14" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="F60" s="23">
         <v>1</v>
       </c>
       <c r="G60" s="9" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H60" s="14"/>
       <c r="I60" s="33">
@@ -3108,19 +3147,19 @@
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B61" s="9" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C61" s="14" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D61" s="54" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E61" s="14" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F61" s="23">
         <v>1</v>
@@ -3141,20 +3180,20 @@
         <v>49</v>
       </c>
       <c r="B62" s="9" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C62" s="14" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D62" s="54"/>
       <c r="E62" s="14" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F62" s="23">
         <v>1</v>
       </c>
       <c r="G62" s="9" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="H62" s="14"/>
       <c r="I62" s="33">
@@ -3169,23 +3208,23 @@
         <v>51</v>
       </c>
       <c r="B63" s="9" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C63" s="14" t="s">
         <v>15</v>
       </c>
       <c r="D63" s="54"/>
       <c r="E63" s="14" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="F63" s="23">
         <v>1</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="H63" s="14" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="I63" s="33">
         <v>5.0499999999999996E-2</v>
@@ -3196,23 +3235,23 @@
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B64" s="10" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C64" s="14" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D64" s="54"/>
       <c r="E64" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F64" s="23">
         <v>1</v>
       </c>
       <c r="G64" s="14" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="H64" s="14"/>
       <c r="I64" s="33">
@@ -3227,14 +3266,14 @@
         <v>48</v>
       </c>
       <c r="B65" s="9" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C65" s="14" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D65" s="54"/>
       <c r="E65" s="14" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F65" s="23">
         <v>1</v>
@@ -3244,31 +3283,31 @@
       </c>
       <c r="H65" s="14"/>
       <c r="I65" s="33">
-        <v>5</v>
+        <v>1.4285714285714285E-2</v>
       </c>
       <c r="J65" s="34">
-        <v>300</v>
+        <v>0.8571428571428571</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B66" s="10" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C66" s="14" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D66" s="54"/>
       <c r="E66" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F66" s="23">
         <v>1</v>
       </c>
       <c r="G66" s="14" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="H66" s="14"/>
       <c r="I66" s="33">
@@ -3283,14 +3322,14 @@
         <v>62</v>
       </c>
       <c r="B67" s="10" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C67" s="14" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D67" s="55"/>
       <c r="E67" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F67" s="23">
         <v>1</v>
@@ -3308,19 +3347,19 @@
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B68" s="10" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C68" s="14" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D68" s="57" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E68" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F68" s="23">
         <v>1</v>
@@ -3338,19 +3377,19 @@
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B69" s="10" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C69" s="14" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D69" s="57" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E69" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F69" s="23">
         <v>1</v>
@@ -3368,23 +3407,23 @@
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B70" s="9" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C70" s="14" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D70" s="54"/>
       <c r="E70" s="14" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F70" s="23">
         <v>1</v>
       </c>
       <c r="G70" s="9" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="H70" s="14"/>
       <c r="I70" s="33">
@@ -3399,18 +3438,18 @@
         <v>53</v>
       </c>
       <c r="B71" s="9" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C71" s="14" t="s">
         <v>15</v>
       </c>
       <c r="D71" s="54"/>
       <c r="E71" s="14" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="F71" s="9"/>
       <c r="G71" s="9" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="H71" s="14"/>
       <c r="I71" s="33">
@@ -3425,20 +3464,20 @@
         <v>57</v>
       </c>
       <c r="B72" s="9" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C72" s="14" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D72" s="54"/>
       <c r="E72" s="14" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F72" s="23">
         <v>1</v>
       </c>
       <c r="G72" s="9" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="H72" s="14"/>
       <c r="I72" s="33">
@@ -3450,19 +3489,19 @@
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B73" s="10" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C73" s="14" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D73" s="57" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E73" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F73" s="23">
         <v>1</v>
@@ -3483,29 +3522,29 @@
         <v>52</v>
       </c>
       <c r="B74" s="9" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C74" s="14" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D74" s="54"/>
       <c r="E74" s="14" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F74" s="23">
         <v>1</v>
       </c>
       <c r="G74" s="9" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="H74" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="I74" s="33">
-        <v>5.0499999999999996E-2</v>
+      <c r="I74" s="63">
+        <v>1.4428571428571428E-4</v>
       </c>
       <c r="J74">
-        <v>3.03</v>
+        <v>8.6571428571428563E-3</v>
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.3">
@@ -3513,18 +3552,18 @@
         <v>58</v>
       </c>
       <c r="B75" s="9" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C75" s="14" t="s">
         <v>15</v>
       </c>
       <c r="D75" s="54"/>
       <c r="E75" s="14" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="F75" s="27"/>
       <c r="G75" s="9" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="H75" s="14"/>
       <c r="I75" s="33">
@@ -3539,20 +3578,20 @@
         <v>60</v>
       </c>
       <c r="B76" s="9" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C76" s="14" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D76" s="54"/>
       <c r="E76" s="14" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F76" s="21">
         <v>1</v>
       </c>
       <c r="G76" s="32" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="H76" s="14"/>
       <c r="I76" s="33">
@@ -3564,19 +3603,19 @@
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B77" s="10" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C77" s="14" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D77" s="57" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E77" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F77" s="21">
         <v>1</v>
@@ -3594,17 +3633,17 @@
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B78" s="9" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C78" s="14" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D78" s="54"/>
       <c r="E78" s="14" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F78" s="23">
         <v>1</v>
@@ -3625,20 +3664,20 @@
         <v>63</v>
       </c>
       <c r="B79" s="9" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C79" s="14" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D79" s="55"/>
       <c r="E79" s="14" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F79" s="23">
         <v>1</v>
       </c>
       <c r="G79" s="32" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="H79" s="14"/>
       <c r="I79" s="33">
@@ -3653,14 +3692,14 @@
         <v>48</v>
       </c>
       <c r="B80" s="10" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C80" s="14" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D80" s="54"/>
       <c r="E80" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F80" s="21">
         <v>1</v>
@@ -3681,14 +3720,14 @@
         <v>56</v>
       </c>
       <c r="B81" s="9" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C81" s="14" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D81" s="54"/>
       <c r="E81" s="14" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F81" s="21">
         <v>1</v>
@@ -3709,18 +3748,18 @@
         <v>64</v>
       </c>
       <c r="B82" s="9" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C82" s="14" t="s">
         <v>15</v>
       </c>
       <c r="D82" s="54"/>
       <c r="E82" s="14" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="F82" s="9"/>
       <c r="G82" s="14" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="H82" s="14"/>
       <c r="I82" s="33">
@@ -3735,24 +3774,22 @@
         <v>65</v>
       </c>
       <c r="B83" s="9" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C83" s="14" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D83" s="54"/>
       <c r="E83" s="14" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F83" s="23">
         <v>1</v>
       </c>
       <c r="G83" s="14" t="s">
-        <v>189</v>
-      </c>
-      <c r="H83" s="14" t="s">
-        <v>213</v>
-      </c>
+        <v>187</v>
+      </c>
+      <c r="H83" s="14"/>
       <c r="I83" s="33">
         <v>5.0499999999999996E-2</v>
       </c>
@@ -3765,14 +3802,14 @@
         <v>59</v>
       </c>
       <c r="B84" s="9" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C84" s="14" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D84" s="54"/>
       <c r="E84" s="14" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F84" s="21">
         <v>1</v>
@@ -3793,20 +3830,20 @@
         <v>66</v>
       </c>
       <c r="B85" s="10" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C85" s="14" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D85" s="54"/>
       <c r="E85" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F85" s="20">
         <v>1</v>
       </c>
       <c r="G85" s="14" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="H85" s="14" t="s">
         <v>55</v>
@@ -3823,20 +3860,20 @@
         <v>54</v>
       </c>
       <c r="B86" s="9" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C86" s="14" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D86" s="54"/>
       <c r="E86" s="14" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F86" s="23">
         <v>1</v>
       </c>
       <c r="G86" s="32" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="H86" s="14"/>
       <c r="I86" s="33">
@@ -3851,16 +3888,16 @@
         <v>61</v>
       </c>
       <c r="B87" s="9" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C87" s="14" t="s">
         <v>18</v>
       </c>
       <c r="D87" s="54" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E87" s="14" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F87" s="21">
         <v>1</v>
@@ -3881,14 +3918,14 @@
         <v>54</v>
       </c>
       <c r="B88" s="10" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C88" s="14" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D88" s="54"/>
       <c r="E88" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F88" s="21">
         <v>1</v>
@@ -3909,20 +3946,20 @@
         <v>68</v>
       </c>
       <c r="B89" s="9" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C89" s="14" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D89" s="54"/>
       <c r="E89" s="14" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="F89" s="23">
         <v>1</v>
       </c>
       <c r="G89" s="32" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="H89" s="14"/>
       <c r="I89" s="33">
@@ -3937,14 +3974,14 @@
         <v>79</v>
       </c>
       <c r="B90" s="9" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C90" s="14" t="s">
         <v>18</v>
       </c>
       <c r="D90" s="55"/>
       <c r="E90" s="14" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F90" s="23">
         <v>1</v>
@@ -3954,9 +3991,9 @@
       </c>
       <c r="H90" s="14"/>
       <c r="I90" s="33">
-        <v>0.01</v>
-      </c>
-      <c r="J90" s="34">
+        <v>6.6666666666666671E-3</v>
+      </c>
+      <c r="J90" s="64">
         <v>0.4</v>
       </c>
     </row>
@@ -3965,14 +4002,14 @@
         <v>68</v>
       </c>
       <c r="B91" s="10" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C91" s="14" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D91" s="55"/>
       <c r="E91" s="14" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="F91" s="23">
         <v>1</v>
@@ -3993,20 +4030,20 @@
         <v>59</v>
       </c>
       <c r="B92" s="9" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C92" s="14" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D92" s="55"/>
       <c r="E92" s="14" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F92" s="23">
         <v>1</v>
       </c>
       <c r="G92" s="32" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="H92" s="14"/>
       <c r="I92" s="33">
@@ -4021,22 +4058,22 @@
         <v>67</v>
       </c>
       <c r="B93" s="9" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C93" s="14" t="s">
         <v>18</v>
       </c>
       <c r="D93" s="54" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E93" s="14" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F93" s="20">
         <v>1</v>
       </c>
       <c r="G93" s="9" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="H93" s="14"/>
       <c r="I93" s="33">
@@ -4051,14 +4088,14 @@
         <v>56</v>
       </c>
       <c r="B94" s="10" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C94" s="14" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D94" s="54"/>
       <c r="E94" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F94" s="21">
         <v>1</v>
@@ -4079,24 +4116,22 @@
         <v>72</v>
       </c>
       <c r="B95" s="9" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C95" s="14" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D95" s="54"/>
       <c r="E95" s="14" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F95" s="23">
         <v>1</v>
       </c>
       <c r="G95" s="9" t="s">
-        <v>189</v>
-      </c>
-      <c r="H95" s="14" t="s">
-        <v>213</v>
-      </c>
+        <v>187</v>
+      </c>
+      <c r="H95" s="14"/>
       <c r="I95" s="46">
         <v>0.05</v>
       </c>
@@ -4106,26 +4141,26 @@
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A96" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B96" s="9" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C96" s="14" t="s">
         <v>70</v>
       </c>
       <c r="D96" s="54"/>
       <c r="E96" s="14" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F96" s="21">
         <v>1</v>
       </c>
       <c r="G96" s="14" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H96" s="14" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="I96" s="33">
         <v>7.3499999999999996E-2</v>
@@ -4139,14 +4174,14 @@
         <v>59</v>
       </c>
       <c r="B97" s="10" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C97" s="14" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D97" s="54"/>
       <c r="E97" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F97" s="23">
         <v>1</v>
@@ -4163,22 +4198,22 @@
       </c>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A98" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="B98" s="10" t="s">
-        <v>162</v>
-      </c>
-      <c r="C98" s="14" t="s">
+      <c r="A98" s="65" t="s">
+        <v>130</v>
+      </c>
+      <c r="B98" s="66" t="s">
+        <v>160</v>
+      </c>
+      <c r="C98" s="67" t="s">
         <v>18</v>
       </c>
       <c r="D98" s="54" t="s">
-        <v>198</v>
-      </c>
-      <c r="E98" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="F98" s="23">
+        <v>196</v>
+      </c>
+      <c r="E98" s="67" t="s">
+        <v>178</v>
+      </c>
+      <c r="F98" s="68">
         <v>1</v>
       </c>
       <c r="G98" s="14" t="s">
@@ -4193,22 +4228,22 @@
       </c>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A99" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="B99" s="10" t="s">
-        <v>162</v>
-      </c>
-      <c r="C99" s="14" t="s">
+      <c r="A99" s="65" t="s">
+        <v>131</v>
+      </c>
+      <c r="B99" s="66" t="s">
+        <v>160</v>
+      </c>
+      <c r="C99" s="67" t="s">
         <v>18</v>
       </c>
       <c r="D99" s="54" t="s">
-        <v>199</v>
-      </c>
-      <c r="E99" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="F99" s="23">
+        <v>197</v>
+      </c>
+      <c r="E99" s="67" t="s">
+        <v>178</v>
+      </c>
+      <c r="F99" s="68">
         <v>1</v>
       </c>
       <c r="G99" s="14" t="s">
@@ -4227,20 +4262,20 @@
         <v>74</v>
       </c>
       <c r="B100" s="9" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C100" s="14" t="s">
         <v>18</v>
       </c>
       <c r="D100" s="54"/>
       <c r="E100" s="14" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F100" s="21">
         <v>1</v>
       </c>
       <c r="G100" s="32" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="H100" s="14"/>
       <c r="I100" s="33">
@@ -4255,23 +4290,23 @@
         <v>71</v>
       </c>
       <c r="B101" s="9" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C101" s="14" t="s">
         <v>70</v>
       </c>
       <c r="D101" s="54"/>
       <c r="E101" s="14" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F101" s="23">
         <v>1</v>
       </c>
       <c r="G101" s="14" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H101" s="14" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="I101" s="33">
         <v>7.3499999999999996E-2</v>
@@ -4281,54 +4316,54 @@
       </c>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A102" s="3" t="s">
+      <c r="A102" s="61" t="s">
         <v>79</v>
       </c>
-      <c r="B102" s="10" t="s">
-        <v>162</v>
-      </c>
-      <c r="C102" s="14" t="s">
+      <c r="B102" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="C102" s="15" t="s">
         <v>18</v>
       </c>
       <c r="D102" s="54"/>
       <c r="E102" s="15" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F102" s="24">
         <v>1</v>
       </c>
-      <c r="G102" s="15" t="s">
+      <c r="G102" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="H102" s="15"/>
+      <c r="H102" s="14"/>
       <c r="I102" s="33">
-        <v>0.03</v>
+        <v>3.3333333333333333E-2</v>
       </c>
       <c r="J102" s="43">
         <v>2</v>
       </c>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A103" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="B103" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="C103" s="14" t="s">
+      <c r="A103" s="65" t="s">
+        <v>132</v>
+      </c>
+      <c r="B103" s="69" t="s">
+        <v>159</v>
+      </c>
+      <c r="C103" s="67" t="s">
         <v>18</v>
       </c>
       <c r="D103" s="54" t="s">
-        <v>199</v>
-      </c>
-      <c r="E103" s="14" t="s">
-        <v>174</v>
-      </c>
-      <c r="F103" s="21">
+        <v>197</v>
+      </c>
+      <c r="E103" s="67" t="s">
+        <v>172</v>
+      </c>
+      <c r="F103" s="70">
         <v>1</v>
       </c>
       <c r="G103" s="32" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="H103" s="14"/>
       <c r="I103" s="33">
@@ -4343,23 +4378,23 @@
         <v>73</v>
       </c>
       <c r="B104" s="9" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C104" s="14" t="s">
         <v>70</v>
       </c>
       <c r="D104" s="54"/>
       <c r="E104" s="14" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F104" s="23">
         <v>1</v>
       </c>
-      <c r="G104" s="9" t="s">
-        <v>209</v>
+      <c r="G104" s="14" t="s">
+        <v>207</v>
       </c>
       <c r="H104" s="14" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="I104" s="33">
         <v>0.128</v>
@@ -4373,22 +4408,22 @@
         <v>67</v>
       </c>
       <c r="B105" s="10" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C105" s="14" t="s">
         <v>18</v>
       </c>
       <c r="D105" s="54" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E105" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F105" s="28">
         <v>1</v>
       </c>
       <c r="G105" s="14" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="H105" s="14"/>
       <c r="I105" s="33">
@@ -4399,26 +4434,26 @@
       </c>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A106" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="B106" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="C106" s="14" t="s">
+      <c r="A106" s="65" t="s">
+        <v>133</v>
+      </c>
+      <c r="B106" s="69" t="s">
+        <v>159</v>
+      </c>
+      <c r="C106" s="67" t="s">
         <v>18</v>
       </c>
       <c r="D106" s="54" t="s">
-        <v>198</v>
-      </c>
-      <c r="E106" s="14" t="s">
-        <v>174</v>
-      </c>
-      <c r="F106" s="28">
+        <v>196</v>
+      </c>
+      <c r="E106" s="67" t="s">
+        <v>172</v>
+      </c>
+      <c r="F106" s="71">
         <v>1</v>
       </c>
       <c r="G106" s="32" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="H106" s="14"/>
       <c r="I106" s="33">
@@ -4433,22 +4468,22 @@
         <v>76</v>
       </c>
       <c r="B107" s="9" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C107" s="14" t="s">
         <v>18</v>
       </c>
       <c r="D107" s="54" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E107" s="14" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F107" s="23">
         <v>1</v>
       </c>
       <c r="G107" s="9" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="H107" s="14"/>
       <c r="I107" s="46">
@@ -4463,20 +4498,20 @@
         <v>75</v>
       </c>
       <c r="B108" s="9" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C108" s="14" t="s">
         <v>70</v>
       </c>
       <c r="D108" s="54"/>
       <c r="E108" s="14" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F108" s="23">
         <v>1</v>
       </c>
       <c r="G108" s="14" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H108" s="14"/>
       <c r="I108" s="33">
@@ -4487,27 +4522,29 @@
       </c>
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A109" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="B109" s="10" t="s">
-        <v>162</v>
-      </c>
-      <c r="C109" s="14" t="s">
-        <v>96</v>
-      </c>
-      <c r="D109" s="54"/>
-      <c r="E109" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="F109" s="21">
+      <c r="A109" s="61" t="s">
+        <v>215</v>
+      </c>
+      <c r="B109" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="C109" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="D109" s="54" t="s">
+        <v>216</v>
+      </c>
+      <c r="E109" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="F109" s="31">
         <v>1</v>
       </c>
       <c r="G109" s="14" t="s">
         <v>55</v>
       </c>
       <c r="H109" s="9" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="I109" s="33">
         <v>0.10483333333333333</v>
@@ -4517,54 +4554,54 @@
       </c>
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A110" s="3" t="s">
+      <c r="A110" s="61" t="s">
         <v>79</v>
       </c>
-      <c r="B110" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="C110" s="14" t="s">
+      <c r="B110" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="C110" s="15" t="s">
         <v>18</v>
       </c>
       <c r="D110" s="54"/>
-      <c r="E110" s="14" t="s">
-        <v>174</v>
-      </c>
-      <c r="F110" s="21">
+      <c r="E110" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="F110" s="31">
         <v>1</v>
       </c>
       <c r="G110" s="14" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="H110" s="14"/>
       <c r="I110" s="33">
-        <v>0.03</v>
+        <v>3.3333333333333333E-2</v>
       </c>
       <c r="J110" s="38">
         <v>2</v>
       </c>
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A111" s="2" t="s">
+      <c r="A111" s="65" t="s">
         <v>75</v>
       </c>
-      <c r="B111" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="C111" s="14" t="s">
-        <v>170</v>
+      <c r="B111" s="69" t="s">
+        <v>162</v>
+      </c>
+      <c r="C111" s="67" t="s">
+        <v>168</v>
       </c>
       <c r="D111" s="54" t="s">
-        <v>201</v>
-      </c>
-      <c r="E111" s="14" t="s">
-        <v>179</v>
-      </c>
-      <c r="F111" s="23">
+        <v>199</v>
+      </c>
+      <c r="E111" s="67" t="s">
+        <v>177</v>
+      </c>
+      <c r="F111" s="68">
         <v>1</v>
       </c>
       <c r="G111" s="9" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="H111" s="14"/>
       <c r="I111" s="33">
@@ -4579,20 +4616,20 @@
         <v>46</v>
       </c>
       <c r="B112" s="10" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C112" s="14" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D112" s="54"/>
       <c r="E112" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F112" s="28">
         <v>1</v>
       </c>
       <c r="G112" s="14" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="H112" s="14"/>
       <c r="I112" s="33">
@@ -4604,23 +4641,23 @@
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A113" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="B113" s="9" t="s">
-        <v>157</v>
+        <v>134</v>
+      </c>
+      <c r="B113" s="62" t="s">
+        <v>177</v>
       </c>
       <c r="C113" s="14" t="s">
         <v>70</v>
       </c>
       <c r="D113" s="54"/>
       <c r="E113" s="14" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F113" s="23">
         <v>1</v>
       </c>
       <c r="G113" s="9" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="H113" s="14"/>
       <c r="I113" s="33">
@@ -4634,21 +4671,21 @@
       <c r="A114" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="B114" s="9" t="s">
-        <v>157</v>
+      <c r="B114" s="62" t="s">
+        <v>177</v>
       </c>
       <c r="C114" s="14" t="s">
         <v>78</v>
       </c>
       <c r="D114" s="54"/>
       <c r="E114" s="14" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="F114" s="23">
         <v>1</v>
       </c>
       <c r="G114" s="9" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="H114" s="14"/>
       <c r="I114" s="33">
@@ -4660,25 +4697,25 @@
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A115" s="6" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="B115" s="10" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C115" s="16" t="s">
         <v>18</v>
       </c>
       <c r="D115" s="58" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E115" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F115" s="29">
         <v>1</v>
       </c>
       <c r="G115" s="47" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="H115" s="16"/>
       <c r="I115" s="48">
@@ -4690,25 +4727,25 @@
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A116" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B116" s="9" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C116" s="14" t="s">
         <v>18</v>
       </c>
       <c r="D116" s="54" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E116" s="14" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F116" s="28">
         <v>1</v>
       </c>
       <c r="G116" s="9" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="H116" s="14"/>
       <c r="I116" s="46">
@@ -4720,7 +4757,7 @@
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A117" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B117" s="9" t="s">
         <v>69</v>
@@ -4730,13 +4767,13 @@
       </c>
       <c r="D117" s="54"/>
       <c r="E117" s="14" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F117" s="23">
         <v>1</v>
       </c>
       <c r="G117" s="14" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="H117" s="14"/>
       <c r="I117" s="33">
@@ -4748,25 +4785,25 @@
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A118" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B118" s="10" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C118" s="14" t="s">
         <v>18</v>
       </c>
       <c r="D118" s="54" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E118" s="14" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F118" s="28">
         <v>1</v>
       </c>
       <c r="G118" s="9" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="H118" s="14"/>
       <c r="I118" s="46">
@@ -4778,25 +4815,25 @@
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A119" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B119" s="9" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C119" s="14" t="s">
         <v>18</v>
       </c>
       <c r="D119" s="54" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E119" s="14" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F119" s="23">
         <v>1</v>
       </c>
       <c r="G119" s="9" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="H119" s="14"/>
       <c r="I119" s="46">
@@ -4811,20 +4848,20 @@
         <v>50</v>
       </c>
       <c r="B120" s="10" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C120" s="14" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D120" s="54"/>
       <c r="E120" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F120" s="23">
         <v>1</v>
       </c>
       <c r="G120" s="14" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="H120" s="14"/>
       <c r="I120" s="33">
@@ -4836,7 +4873,7 @@
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A121" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B121" s="9" t="s">
         <v>69</v>
@@ -4846,13 +4883,13 @@
       </c>
       <c r="D121" s="54"/>
       <c r="E121" s="14" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F121" s="28">
         <v>1</v>
       </c>
       <c r="G121" s="14" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H121" s="14"/>
       <c r="I121" s="33">
@@ -4867,25 +4904,25 @@
         <v>67</v>
       </c>
       <c r="B122" s="9" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C122" s="14" t="s">
         <v>18</v>
       </c>
       <c r="D122" s="54" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E122" s="14" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F122" s="21">
         <v>1</v>
       </c>
       <c r="G122" s="9" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="H122" s="14" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="I122" s="46">
         <v>9.0000000000000011E-2</v>
@@ -4896,26 +4933,26 @@
     </row>
     <row r="123" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A123" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B123" s="9" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C123" s="14" t="s">
         <v>70</v>
       </c>
       <c r="D123" s="54"/>
       <c r="E123" s="14" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F123" s="23">
         <v>1</v>
       </c>
       <c r="G123" s="14" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H123" s="14" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="I123" s="33">
         <v>6.0499999999999998E-2</v>
@@ -4926,23 +4963,23 @@
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A124" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B124" s="9" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C124" s="14" t="s">
         <v>70</v>
       </c>
       <c r="D124" s="54"/>
       <c r="E124" s="14" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F124" s="21">
         <v>1</v>
       </c>
       <c r="G124" s="14" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="H124" s="14"/>
       <c r="I124" s="33">
@@ -4954,23 +4991,23 @@
     </row>
     <row r="125" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A125" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="B125" s="9" t="s">
-        <v>157</v>
+        <v>85</v>
+      </c>
+      <c r="B125" s="62" t="s">
+        <v>177</v>
       </c>
       <c r="C125" s="14" t="s">
         <v>78</v>
       </c>
       <c r="D125" s="54"/>
       <c r="E125" s="14" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="F125" s="28">
         <v>1</v>
       </c>
       <c r="G125" s="9" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="H125" s="14"/>
       <c r="I125" s="33">
@@ -4981,29 +5018,29 @@
       </c>
     </row>
     <row r="126" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A126" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="B126" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="C126" s="14" t="s">
-        <v>96</v>
+      <c r="A126" s="61" t="s">
+        <v>215</v>
+      </c>
+      <c r="B126" s="69" t="s">
+        <v>159</v>
+      </c>
+      <c r="C126" s="67" t="s">
+        <v>95</v>
       </c>
       <c r="D126" s="54" t="s">
-        <v>215</v>
-      </c>
-      <c r="E126" s="14" t="s">
-        <v>174</v>
-      </c>
-      <c r="F126" s="21">
+        <v>216</v>
+      </c>
+      <c r="E126" s="67" t="s">
+        <v>172</v>
+      </c>
+      <c r="F126" s="70">
         <v>1</v>
       </c>
       <c r="G126" s="9" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="H126" s="14" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="I126" s="46">
         <v>0.10483333333333333</v>
@@ -5017,23 +5054,23 @@
         <v>71</v>
       </c>
       <c r="B127" s="9" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C127" s="14" t="s">
         <v>70</v>
       </c>
       <c r="D127" s="54"/>
       <c r="E127" s="14" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F127" s="21">
         <v>1</v>
       </c>
       <c r="G127" s="14" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H127" s="14" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="I127" s="33">
         <v>7.3499999999999996E-2</v>
@@ -5047,20 +5084,20 @@
         <v>75</v>
       </c>
       <c r="B128" s="9" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C128" s="14" t="s">
         <v>70</v>
       </c>
       <c r="D128" s="54"/>
       <c r="E128" s="14" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F128" s="21">
         <v>1</v>
       </c>
       <c r="G128" s="14" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="H128" s="14"/>
       <c r="I128" s="33">
@@ -5072,25 +5109,25 @@
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A129" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B129" s="9" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C129" s="14" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D129" s="54" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E129" s="14" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F129" s="28">
         <v>1</v>
       </c>
       <c r="G129" s="14" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="H129" s="14"/>
       <c r="I129" s="33">
@@ -5102,53 +5139,53 @@
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A130" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="B130" s="9" t="s">
-        <v>157</v>
+        <v>86</v>
+      </c>
+      <c r="B130" s="62" t="s">
+        <v>177</v>
       </c>
       <c r="C130" s="14" t="s">
         <v>78</v>
       </c>
       <c r="D130" s="54"/>
       <c r="E130" s="14" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="F130" s="20">
         <v>1</v>
       </c>
       <c r="G130" s="9" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="H130" s="14"/>
       <c r="I130" s="33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J130" s="43">
-        <v>120</v>
+        <v>60</v>
       </c>
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A131" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B131" s="9" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C131" s="14" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D131" s="54" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E131" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F131" s="23">
         <v>1</v>
       </c>
       <c r="G131" s="14" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="H131" s="14"/>
       <c r="I131" s="33">
@@ -5160,23 +5197,23 @@
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A132" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="B132" s="9" t="s">
-        <v>157</v>
+        <v>134</v>
+      </c>
+      <c r="B132" s="72" t="s">
+        <v>178</v>
       </c>
       <c r="C132" s="14" t="s">
         <v>70</v>
       </c>
       <c r="D132" s="54"/>
       <c r="E132" s="14" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F132" s="28">
         <v>1</v>
       </c>
       <c r="G132" s="14" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="H132" s="14"/>
       <c r="I132" s="33">
@@ -5187,26 +5224,26 @@
       </c>
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A133" s="2" t="s">
+      <c r="A133" s="65" t="s">
         <v>75</v>
       </c>
-      <c r="B133" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="C133" s="14" t="s">
-        <v>170</v>
+      <c r="B133" s="69" t="s">
+        <v>165</v>
+      </c>
+      <c r="C133" s="67" t="s">
+        <v>168</v>
       </c>
       <c r="D133" s="54" t="s">
-        <v>201</v>
-      </c>
-      <c r="E133" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="F133" s="28">
+        <v>199</v>
+      </c>
+      <c r="E133" s="67" t="s">
+        <v>178</v>
+      </c>
+      <c r="F133" s="71">
         <v>1</v>
       </c>
       <c r="G133" s="9" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="H133" s="14"/>
       <c r="I133" s="33">
@@ -5220,21 +5257,21 @@
       <c r="A134" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B134" s="9" t="s">
-        <v>157</v>
+      <c r="B134" s="62" t="s">
+        <v>177</v>
       </c>
       <c r="C134" s="14" t="s">
         <v>78</v>
       </c>
       <c r="D134" s="54"/>
       <c r="E134" s="14" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F134" s="28">
         <v>1</v>
       </c>
       <c r="G134" s="9" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="H134" s="14"/>
       <c r="I134" s="46">
@@ -5246,25 +5283,25 @@
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A135" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B135" s="9" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C135" s="14" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D135" s="54" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E135" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F135" s="28">
         <v>1</v>
       </c>
       <c r="G135" s="14" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="H135" s="14"/>
       <c r="I135" s="33">
@@ -5276,30 +5313,30 @@
     </row>
     <row r="136" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A136" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B136" s="9" t="s">
-        <v>157</v>
+        <v>177</v>
       </c>
       <c r="C136" s="14" t="s">
         <v>78</v>
       </c>
       <c r="D136" s="54"/>
       <c r="E136" s="14" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F136" s="28">
         <v>1</v>
       </c>
       <c r="G136" s="9" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="H136" s="14"/>
       <c r="I136" s="46">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J136" s="42">
-        <v>120</v>
+        <v>30</v>
       </c>
     </row>
     <row r="137" spans="1:10" x14ac:dyDescent="0.3">
@@ -5307,20 +5344,20 @@
         <v>77</v>
       </c>
       <c r="B137" s="9" t="s">
-        <v>157</v>
+        <v>178</v>
       </c>
       <c r="C137" s="14" t="s">
         <v>78</v>
       </c>
       <c r="D137" s="54"/>
       <c r="E137" s="14" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="F137" s="28">
         <v>1</v>
       </c>
       <c r="G137" s="9" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="H137" s="14"/>
       <c r="I137" s="33">
@@ -5332,25 +5369,25 @@
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A138" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B138" s="9" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C138" s="14" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D138" s="54" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E138" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F138" s="28">
         <v>1</v>
       </c>
       <c r="G138" s="14" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="H138" s="14"/>
       <c r="I138" s="33">
@@ -5362,25 +5399,25 @@
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A139" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B139" s="9" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C139" s="14" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D139" s="54" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E139" s="14" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F139" s="28">
         <v>1</v>
       </c>
       <c r="G139" s="14" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="H139" s="14"/>
       <c r="I139" s="46">
@@ -5392,23 +5429,23 @@
     </row>
     <row r="140" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A140" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B140" s="9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C140" s="14" t="s">
         <v>78</v>
       </c>
       <c r="D140" s="54"/>
       <c r="E140" s="14" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F140" s="28">
         <v>1</v>
       </c>
       <c r="G140" s="14" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H140" s="14"/>
       <c r="I140" s="33">
@@ -5420,25 +5457,25 @@
     </row>
     <row r="141" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A141" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B141" s="9" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C141" s="14" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D141" s="54" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E141" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F141" s="28">
         <v>1</v>
       </c>
       <c r="G141" s="14" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="H141" s="14"/>
       <c r="I141" s="33">
@@ -5450,25 +5487,25 @@
     </row>
     <row r="142" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A142" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B142" s="9" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C142" s="14" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D142" s="54" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E142" s="14" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F142" s="28">
         <v>1</v>
       </c>
       <c r="G142" s="14" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="H142" s="14"/>
       <c r="I142" s="33">
@@ -5480,23 +5517,23 @@
     </row>
     <row r="143" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A143" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B143" s="9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C143" s="14" t="s">
         <v>78</v>
       </c>
       <c r="D143" s="54"/>
       <c r="E143" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F143" s="28">
         <v>1</v>
       </c>
       <c r="G143" s="9" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="H143" s="14"/>
       <c r="I143" s="33">
@@ -5508,25 +5545,25 @@
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A144" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B144" s="9" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C144" s="14" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D144" s="54" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E144" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F144" s="28">
         <v>1</v>
       </c>
       <c r="G144" s="14" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="H144" s="14"/>
       <c r="I144" s="33">
@@ -5538,25 +5575,25 @@
     </row>
     <row r="145" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A145" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B145" s="9" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C145" s="14" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D145" s="54" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E145" s="14" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F145" s="21">
         <v>1</v>
       </c>
       <c r="G145" s="9" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="H145" s="14"/>
       <c r="I145" s="33">
@@ -5568,23 +5605,23 @@
     </row>
     <row r="146" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A146" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B146" s="9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C146" s="14" t="s">
         <v>78</v>
       </c>
       <c r="D146" s="54"/>
       <c r="E146" s="14" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F146" s="23">
         <v>1</v>
       </c>
       <c r="G146" s="9" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="H146" s="14"/>
       <c r="I146" s="33">
@@ -5596,25 +5633,25 @@
     </row>
     <row r="147" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A147" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B147" s="9" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C147" s="14" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D147" s="54" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E147" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F147" s="28">
         <v>1</v>
       </c>
       <c r="G147" s="32" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H147" s="14"/>
       <c r="I147" s="33">
@@ -5626,25 +5663,25 @@
     </row>
     <row r="148" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A148" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B148" s="9" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C148" s="14" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D148" s="54" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E148" s="14" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F148" s="21">
         <v>1</v>
       </c>
       <c r="G148" s="32" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H148" s="14"/>
       <c r="I148" s="33">
@@ -5656,23 +5693,23 @@
     </row>
     <row r="149" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A149" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B149" s="9" t="s">
-        <v>157</v>
+        <v>178</v>
       </c>
       <c r="C149" s="14" t="s">
         <v>78</v>
       </c>
       <c r="D149" s="54"/>
       <c r="E149" s="14" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="F149" s="28">
         <v>1</v>
       </c>
       <c r="G149" s="9" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="H149" s="14"/>
       <c r="I149" s="33">
@@ -5684,25 +5721,25 @@
     </row>
     <row r="150" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A150" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B150" s="9" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C150" s="17" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D150" s="54" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E150" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F150" s="21">
         <v>1</v>
       </c>
       <c r="G150" s="17" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="H150" s="17"/>
       <c r="I150" s="50">
@@ -5714,25 +5751,25 @@
     </row>
     <row r="151" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A151" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B151" s="9" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C151" s="14" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D151" s="54" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E151" s="14" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F151" s="28">
         <v>1</v>
       </c>
       <c r="G151" s="14" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="H151" s="14"/>
       <c r="I151" s="46">
@@ -5744,53 +5781,53 @@
     </row>
     <row r="152" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A152" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B152" s="9" t="s">
-        <v>157</v>
+        <v>178</v>
       </c>
       <c r="C152" s="14" t="s">
         <v>78</v>
       </c>
       <c r="D152" s="54"/>
       <c r="E152" s="14" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="F152" s="28">
         <v>1</v>
       </c>
       <c r="G152" s="9" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="H152" s="14"/>
       <c r="I152" s="33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J152" s="49">
-        <v>120</v>
+        <v>60</v>
       </c>
     </row>
     <row r="153" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A153" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B153" s="9" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C153" s="17" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D153" s="54" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E153" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F153" s="28">
         <v>1</v>
       </c>
       <c r="G153" s="17" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="H153" s="14"/>
       <c r="I153" s="46">
@@ -5802,25 +5839,25 @@
     </row>
     <row r="154" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A154" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B154" s="9" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C154" s="14" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D154" s="54" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E154" s="14" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F154" s="21">
         <v>1</v>
       </c>
       <c r="G154" s="14" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="H154" s="14"/>
       <c r="I154" s="33">
@@ -5832,23 +5869,23 @@
     </row>
     <row r="155" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A155" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B155" s="9" t="s">
-        <v>157</v>
+        <v>178</v>
       </c>
       <c r="C155" s="14" t="s">
         <v>78</v>
       </c>
       <c r="D155" s="54"/>
       <c r="E155" s="14" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="F155" s="28">
         <v>1</v>
       </c>
       <c r="G155" s="9" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="H155" s="14"/>
       <c r="I155" s="33">
@@ -5860,25 +5897,25 @@
     </row>
     <row r="156" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A156" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B156" s="9" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C156" s="14" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D156" s="54" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E156" s="14" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F156" s="28">
         <v>1</v>
       </c>
       <c r="G156" s="9" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="H156" s="14"/>
       <c r="I156" s="33">
@@ -5890,23 +5927,23 @@
     </row>
     <row r="157" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A157" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B157" s="9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C157" s="14" t="s">
         <v>78</v>
       </c>
       <c r="D157" s="54"/>
       <c r="E157" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F157" s="28">
         <v>1</v>
       </c>
       <c r="G157" s="9" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="H157" s="14"/>
       <c r="I157" s="33">
@@ -5918,25 +5955,25 @@
     </row>
     <row r="158" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A158" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B158" s="9" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C158" s="17" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D158" s="54" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E158" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F158" s="28">
         <v>1</v>
       </c>
       <c r="G158" s="14" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="H158" s="14"/>
       <c r="I158" s="46">
@@ -5948,25 +5985,25 @@
     </row>
     <row r="159" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A159" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B159" s="9" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C159" s="14" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D159" s="54" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E159" s="14" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F159" s="21">
         <v>1</v>
       </c>
       <c r="G159" s="32" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H159" s="14"/>
       <c r="I159" s="33">
@@ -5981,50 +6018,50 @@
         <v>53</v>
       </c>
       <c r="B160" s="9" t="s">
-        <v>157</v>
+        <v>178</v>
       </c>
       <c r="C160" s="14" t="s">
         <v>78</v>
       </c>
       <c r="D160" s="54"/>
       <c r="E160" s="14" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F160" s="28">
         <v>1</v>
       </c>
       <c r="G160" s="9" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="H160" s="14"/>
       <c r="I160" s="33">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J160" s="51">
-        <v>180</v>
+        <v>120</v>
       </c>
     </row>
     <row r="161" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A161" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B161" s="9" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C161" s="17" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D161" s="59" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E161" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F161" s="20">
         <v>1</v>
       </c>
       <c r="G161" s="14" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="H161" s="14"/>
       <c r="I161" s="46">
@@ -6036,23 +6073,23 @@
     </row>
     <row r="162" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A162" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="B162" s="9" t="s">
-        <v>157</v>
+        <v>91</v>
+      </c>
+      <c r="B162" s="62" t="s">
+        <v>177</v>
       </c>
       <c r="C162" s="14" t="s">
         <v>78</v>
       </c>
       <c r="D162" s="54"/>
       <c r="E162" s="14" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="F162" s="23">
         <v>1</v>
       </c>
       <c r="G162" s="9" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="H162" s="14"/>
       <c r="I162" s="33">
@@ -6064,53 +6101,53 @@
     </row>
     <row r="163" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A163" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B163" s="9" t="s">
-        <v>157</v>
+        <v>178</v>
       </c>
       <c r="C163" s="14" t="s">
         <v>78</v>
       </c>
       <c r="D163" s="54"/>
       <c r="E163" s="14" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F163" s="28">
         <v>1</v>
       </c>
       <c r="G163" s="9" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="H163" s="14"/>
       <c r="I163" s="33">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="J163" s="51">
-        <v>180</v>
+        <v>30</v>
       </c>
     </row>
     <row r="164" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A164" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B164" s="9" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C164" s="17" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D164" s="59" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E164" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F164" s="21">
         <v>1</v>
       </c>
       <c r="G164" s="14" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="H164" s="14"/>
       <c r="I164" s="46">
@@ -6122,7 +6159,7 @@
     </row>
     <row r="165" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A165" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B165" s="9" t="s">
         <v>69</v>
@@ -6132,13 +6169,13 @@
       </c>
       <c r="D165" s="54"/>
       <c r="E165" s="14" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F165" s="23">
         <v>1</v>
       </c>
       <c r="G165" s="14" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H165" s="14"/>
       <c r="I165" s="33">
@@ -6150,23 +6187,23 @@
     </row>
     <row r="166" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A166" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B166" s="9" t="s">
-        <v>157</v>
+        <v>178</v>
       </c>
       <c r="C166" s="14" t="s">
         <v>78</v>
       </c>
       <c r="D166" s="54"/>
       <c r="E166" s="14" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="F166" s="28">
         <v>1</v>
       </c>
       <c r="G166" s="9" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="H166" s="14"/>
       <c r="I166" s="33">
@@ -6178,25 +6215,25 @@
     </row>
     <row r="167" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A167" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B167" s="9" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C167" s="17" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D167" s="59" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E167" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F167" s="23">
         <v>1</v>
       </c>
       <c r="G167" s="32" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H167" s="14"/>
       <c r="I167" s="46">
@@ -6208,7 +6245,7 @@
     </row>
     <row r="168" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A168" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B168" s="9" t="s">
         <v>69</v>
@@ -6218,16 +6255,16 @@
       </c>
       <c r="D168" s="54"/>
       <c r="E168" s="14" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F168" s="21">
         <v>1</v>
       </c>
       <c r="G168" s="14" t="s">
-        <v>184</v>
-      </c>
-      <c r="H168" s="14" t="s">
-        <v>209</v>
+        <v>182</v>
+      </c>
+      <c r="H168" s="9" t="s">
+        <v>207</v>
       </c>
       <c r="I168" s="33">
         <v>9.6000000000000002E-2</v>
@@ -6237,26 +6274,26 @@
       </c>
     </row>
     <row r="169" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A169" s="3" t="s">
+      <c r="A169" s="61" t="s">
         <v>45</v>
       </c>
-      <c r="B169" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="C169" s="14" t="s">
+      <c r="B169" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="C169" s="15" t="s">
         <v>78</v>
       </c>
       <c r="D169" s="54"/>
       <c r="E169" s="15" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F169" s="30">
         <v>1</v>
       </c>
-      <c r="G169" s="11" t="s">
-        <v>185</v>
-      </c>
-      <c r="H169" s="15"/>
+      <c r="G169" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="H169" s="14"/>
       <c r="I169" s="35">
         <v>2.8333333333333332E-2</v>
       </c>
@@ -6266,23 +6303,23 @@
     </row>
     <row r="170" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A170" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B170" s="62" t="s">
+        <v>177</v>
+      </c>
+      <c r="C170" s="14" t="s">
         <v>95</v>
-      </c>
-      <c r="B170" s="9" t="s">
-        <v>157</v>
-      </c>
-      <c r="C170" s="14" t="s">
-        <v>96</v>
       </c>
       <c r="D170" s="54"/>
       <c r="E170" s="14" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F170" s="23">
         <v>1</v>
       </c>
       <c r="G170" s="9" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="H170" s="14"/>
       <c r="I170" s="33">
@@ -6294,28 +6331,28 @@
     </row>
     <row r="171" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A171" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B171" s="9" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C171" s="14" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D171" s="54" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E171" s="14" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F171" s="21">
         <v>1</v>
       </c>
       <c r="G171" s="14" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="H171" s="32" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="I171" s="33">
         <v>7.2333333333333333E-2</v>
@@ -6326,26 +6363,26 @@
     </row>
     <row r="172" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A172" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B172" s="9" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C172" s="14" t="s">
         <v>70</v>
       </c>
       <c r="D172" s="54"/>
       <c r="E172" s="14" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F172" s="28">
         <v>0.4</v>
       </c>
       <c r="G172" s="9" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H172" s="14" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="I172" s="33">
         <v>7.2333333333333333E-2</v>
@@ -6356,23 +6393,23 @@
     </row>
     <row r="173" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A173" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B173" s="9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C173" s="14" t="s">
         <v>78</v>
       </c>
       <c r="D173" s="54"/>
       <c r="E173" s="14" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F173" s="28">
         <v>1</v>
       </c>
       <c r="G173" s="9" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="H173" s="14"/>
       <c r="I173" s="33">
@@ -6384,26 +6421,26 @@
     </row>
     <row r="174" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A174" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B174" s="9" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C174" s="14" t="s">
         <v>70</v>
       </c>
       <c r="D174" s="54"/>
       <c r="E174" s="14" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F174" s="28">
         <v>0.6</v>
       </c>
       <c r="G174" s="9" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H174" s="14" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="I174" s="33">
         <v>7.2333333333333333E-2</v>
@@ -6414,26 +6451,26 @@
     </row>
     <row r="175" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A175" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B175" s="9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C175" s="14" t="s">
         <v>78</v>
       </c>
       <c r="D175" s="54"/>
       <c r="E175" s="14" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F175" s="28">
         <v>1</v>
       </c>
       <c r="G175" s="14" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H175" s="9" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="I175" s="33">
         <v>9.6000000000000002E-2</v>
@@ -6444,25 +6481,25 @@
     </row>
     <row r="176" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A176" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B176" s="9" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C176" s="14" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D176" s="54" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E176" s="14" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F176" s="28">
         <v>1</v>
       </c>
       <c r="G176" s="9" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="H176" s="14"/>
       <c r="I176" s="33">
@@ -6477,23 +6514,23 @@
         <v>71</v>
       </c>
       <c r="B177" s="9" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C177" s="14" t="s">
         <v>70</v>
       </c>
       <c r="D177" s="54"/>
       <c r="E177" s="14" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F177" s="21">
         <v>0.4</v>
       </c>
       <c r="G177" s="32" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H177" s="14" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="I177" s="33">
         <v>6.3166666666666663E-2</v>
@@ -6504,25 +6541,25 @@
     </row>
     <row r="178" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A178" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B178" s="10" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C178" s="14" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D178" s="54" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E178" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F178" s="21">
         <v>1</v>
       </c>
       <c r="G178" s="9" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="H178" s="14"/>
       <c r="I178" s="33">
@@ -6534,23 +6571,23 @@
     </row>
     <row r="179" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A179" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B179" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="C179" s="14" t="s">
         <v>95</v>
-      </c>
-      <c r="B179" s="9" t="s">
-        <v>157</v>
-      </c>
-      <c r="C179" s="14" t="s">
-        <v>96</v>
       </c>
       <c r="D179" s="54"/>
       <c r="E179" s="14" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F179" s="21">
         <v>1</v>
       </c>
       <c r="G179" s="9" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="H179" s="14"/>
       <c r="I179" s="33">
@@ -6562,25 +6599,25 @@
     </row>
     <row r="180" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A180" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B180" s="9" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C180" s="14" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D180" s="54" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E180" s="14" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F180" s="23">
         <v>1</v>
       </c>
       <c r="G180" s="9" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="H180" s="14"/>
       <c r="I180" s="33">
@@ -6595,23 +6632,23 @@
         <v>71</v>
       </c>
       <c r="B181" s="9" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C181" s="14" t="s">
         <v>70</v>
       </c>
       <c r="D181" s="54"/>
       <c r="E181" s="14" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F181" s="23">
         <v>0.6</v>
       </c>
       <c r="G181" s="32" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H181" s="14" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="I181" s="33">
         <v>6.3166666666666663E-2</v>
@@ -6622,25 +6659,25 @@
     </row>
     <row r="182" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A182" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B182" s="9" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C182" s="14" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D182" s="54" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E182" s="14" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F182" s="23">
         <v>1</v>
       </c>
-      <c r="G182" s="9" t="s">
-        <v>209</v>
+      <c r="G182" s="14" t="s">
+        <v>207</v>
       </c>
       <c r="H182" s="14"/>
       <c r="I182" s="33">
@@ -6655,23 +6692,23 @@
         <v>73</v>
       </c>
       <c r="B183" s="9" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C183" s="14" t="s">
         <v>70</v>
       </c>
       <c r="D183" s="54"/>
       <c r="E183" s="14" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F183" s="23">
         <v>0.6</v>
       </c>
       <c r="G183" s="9" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="H183" s="14" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="I183" s="33">
         <v>0.128</v>
@@ -6682,25 +6719,25 @@
     </row>
     <row r="184" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A184" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B184" s="9" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C184" s="14" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D184" s="54" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E184" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F184" s="21">
         <v>1</v>
       </c>
       <c r="G184" s="14" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="H184" s="14"/>
       <c r="I184" s="33">
@@ -6712,25 +6749,25 @@
     </row>
     <row r="185" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A185" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B185" s="9" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C185" s="14" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D185" s="54" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E185" s="14" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F185" s="23">
         <v>1</v>
       </c>
       <c r="G185" s="32" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H185" s="14"/>
       <c r="I185" s="33">
@@ -6745,20 +6782,20 @@
         <v>24</v>
       </c>
       <c r="B186" s="9" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C186" s="14" t="s">
         <v>70</v>
       </c>
       <c r="D186" s="54"/>
       <c r="E186" s="14" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F186" s="21">
         <v>1</v>
       </c>
       <c r="G186" s="9" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="H186" s="14"/>
       <c r="I186" s="33">
@@ -6770,25 +6807,25 @@
     </row>
     <row r="187" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A187" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B187" s="9" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C187" s="14" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D187" s="54" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E187" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F187" s="23">
         <v>1</v>
       </c>
       <c r="G187" s="14" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="H187" s="14"/>
       <c r="I187" s="33">
@@ -6800,25 +6837,25 @@
     </row>
     <row r="188" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A188" s="8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B188" s="13" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C188" s="17" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D188" s="60" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E188" s="17" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F188" s="21">
         <v>1</v>
       </c>
       <c r="G188" s="17" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="H188" s="17"/>
       <c r="I188" s="50">
@@ -6833,20 +6870,20 @@
         <v>29</v>
       </c>
       <c r="B189" s="9" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C189" s="14" t="s">
         <v>70</v>
       </c>
       <c r="D189" s="54"/>
       <c r="E189" s="14" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F189" s="21">
         <v>1</v>
       </c>
       <c r="G189" s="9" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="H189" s="14"/>
       <c r="I189" s="33">
@@ -6858,25 +6895,25 @@
     </row>
     <row r="190" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A190" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B190" s="10" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C190" s="14" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D190" s="54" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E190" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F190" s="21">
         <v>1</v>
       </c>
       <c r="G190" s="14" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="H190" s="14"/>
       <c r="I190" s="33">
@@ -6887,29 +6924,29 @@
       </c>
     </row>
     <row r="191" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A191" s="2" t="s">
-        <v>141</v>
+      <c r="A191" s="61" t="s">
+        <v>140</v>
       </c>
       <c r="B191" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="C191" s="15" t="s">
         <v>169</v>
       </c>
-      <c r="C191" s="15" t="s">
-        <v>171</v>
-      </c>
       <c r="D191" s="59" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E191" s="15" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F191" s="31">
         <v>1</v>
       </c>
-      <c r="G191" s="15" t="s">
-        <v>192</v>
-      </c>
-      <c r="H191" s="15" t="s">
-        <v>193</v>
+      <c r="G191" s="17" t="s">
+        <v>190</v>
+      </c>
+      <c r="H191" s="14" t="s">
+        <v>191</v>
       </c>
       <c r="I191" s="35">
         <v>7.2333333333333333E-2</v>
@@ -6920,23 +6957,23 @@
     </row>
     <row r="192" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A192" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B192" s="9" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C192" s="14" t="s">
         <v>70</v>
       </c>
       <c r="D192" s="54"/>
       <c r="E192" s="14" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F192" s="23">
         <v>1</v>
       </c>
       <c r="G192" s="9" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="H192" s="14"/>
       <c r="I192" s="33">
@@ -6948,28 +6985,28 @@
     </row>
     <row r="193" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A193" s="2" t="s">
-        <v>80</v>
+        <v>217</v>
       </c>
       <c r="B193" s="10" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C193" s="14" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D193" s="54" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E193" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F193" s="21">
         <v>1</v>
       </c>
       <c r="G193" s="14" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="H193" s="9" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="I193" s="33">
         <v>0.10483333333333333</v>
@@ -6980,23 +7017,23 @@
     </row>
     <row r="194" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A194" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B194" s="9" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C194" s="14" t="s">
         <v>70</v>
       </c>
       <c r="D194" s="54"/>
       <c r="E194" s="14" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F194" s="23">
         <v>1</v>
       </c>
       <c r="G194" s="9" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="H194" s="14"/>
       <c r="I194" s="33">
@@ -7007,26 +7044,26 @@
       </c>
     </row>
     <row r="195" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A195" s="2" t="s">
+      <c r="A195" s="65" t="s">
         <v>75</v>
       </c>
-      <c r="B195" s="9" t="s">
-        <v>166</v>
-      </c>
-      <c r="C195" s="14" t="s">
-        <v>170</v>
+      <c r="B195" s="69" t="s">
+        <v>164</v>
+      </c>
+      <c r="C195" s="67" t="s">
+        <v>168</v>
       </c>
       <c r="D195" s="54" t="s">
-        <v>201</v>
-      </c>
-      <c r="E195" s="14" t="s">
-        <v>174</v>
-      </c>
-      <c r="F195" s="23">
+        <v>199</v>
+      </c>
+      <c r="E195" s="67" t="s">
+        <v>172</v>
+      </c>
+      <c r="F195" s="68">
         <v>1</v>
       </c>
       <c r="G195" s="9" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="H195" s="14"/>
       <c r="I195" s="33">
@@ -7041,20 +7078,20 @@
         <v>77</v>
       </c>
       <c r="B196" s="9" t="s">
-        <v>157</v>
+        <v>214</v>
       </c>
       <c r="C196" s="14" t="s">
         <v>78</v>
       </c>
       <c r="D196" s="54"/>
       <c r="E196" s="14" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="F196" s="21">
         <v>1</v>
       </c>
       <c r="G196" s="9" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="H196" s="14"/>
       <c r="I196" s="33">
@@ -7066,25 +7103,25 @@
     </row>
     <row r="197" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A197" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B197" s="9" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C197" s="14" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D197" s="59" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E197" s="14" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F197" s="23">
         <v>1</v>
       </c>
       <c r="G197" s="9" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="H197" s="14"/>
       <c r="I197" s="33">
@@ -7096,25 +7133,25 @@
     </row>
     <row r="198" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A198" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B198" s="9" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C198" s="14" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D198" s="59" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E198" s="14" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F198" s="21">
         <v>1</v>
       </c>
       <c r="G198" s="9" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="H198" s="14"/>
       <c r="I198" s="33">
@@ -7126,23 +7163,23 @@
     </row>
     <row r="199" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A199" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B199" s="9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C199" s="14" t="s">
         <v>78</v>
       </c>
       <c r="D199" s="54"/>
       <c r="E199" s="14" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F199" s="23">
         <v>1</v>
       </c>
       <c r="G199" s="9" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="H199" s="14"/>
       <c r="I199" s="33">
@@ -7154,25 +7191,25 @@
     </row>
     <row r="200" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A200" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B200" s="9" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C200" s="14" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D200" s="59" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E200" s="14" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F200" s="23">
         <v>1</v>
       </c>
-      <c r="G200" s="9" t="s">
-        <v>209</v>
+      <c r="G200" s="14" t="s">
+        <v>207</v>
       </c>
       <c r="H200" s="14"/>
       <c r="I200" s="33">
@@ -7184,25 +7221,25 @@
     </row>
     <row r="201" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A201" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B201" s="9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C201" s="14" t="s">
         <v>78</v>
       </c>
       <c r="D201" s="54" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="E201" s="14" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F201" s="23">
         <v>0.6</v>
       </c>
       <c r="G201" s="32" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="H201" s="14"/>
       <c r="I201" s="33">
@@ -7214,25 +7251,25 @@
     </row>
     <row r="202" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A202" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B202" s="9" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C202" s="14" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D202" s="59" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E202" s="14" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F202" s="23">
         <v>1</v>
       </c>
       <c r="G202" s="32" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H202" s="14"/>
       <c r="I202" s="33">
@@ -7244,23 +7281,23 @@
     </row>
     <row r="203" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A203" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B203" s="9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C203" s="14" t="s">
         <v>78</v>
       </c>
       <c r="D203" s="54"/>
       <c r="E203" s="14" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F203" s="23">
         <v>0.4</v>
       </c>
       <c r="G203" s="9" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="H203" s="14"/>
       <c r="I203" s="33">
@@ -7272,23 +7309,23 @@
     </row>
     <row r="204" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A204" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B204" s="9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C204" s="14" t="s">
         <v>78</v>
       </c>
       <c r="D204" s="54"/>
       <c r="E204" s="14" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F204" s="23">
         <v>0.6</v>
       </c>
       <c r="G204" s="9" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="H204" s="14"/>
       <c r="I204" s="33">
@@ -7300,23 +7337,23 @@
     </row>
     <row r="205" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A205" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B205" s="9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C205" s="14" t="s">
         <v>78</v>
       </c>
       <c r="D205" s="54"/>
       <c r="E205" s="14" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F205" s="21">
         <v>0.6</v>
       </c>
       <c r="G205" s="32" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H205" s="14"/>
       <c r="I205" s="33">
@@ -7328,79 +7365,79 @@
     </row>
     <row r="206" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A206" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B206" s="9" t="s">
-        <v>157</v>
+        <v>214</v>
       </c>
       <c r="C206" s="14" t="s">
         <v>78</v>
       </c>
       <c r="D206" s="54"/>
       <c r="E206" s="14" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="F206" s="23">
         <v>1</v>
       </c>
       <c r="G206" s="9" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="H206" s="14"/>
       <c r="I206" s="33">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J206" s="44">
-        <v>180</v>
+        <v>120</v>
       </c>
     </row>
     <row r="207" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A207" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B207" s="9" t="s">
-        <v>157</v>
+        <v>214</v>
       </c>
       <c r="C207" s="14" t="s">
         <v>78</v>
       </c>
       <c r="D207" s="54"/>
       <c r="E207" s="14" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="F207" s="23">
         <v>1</v>
       </c>
       <c r="G207" s="9" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="H207" s="14"/>
       <c r="I207" s="33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J207" s="44">
-        <v>120</v>
+        <v>60</v>
       </c>
     </row>
     <row r="208" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A208" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B208" s="9" t="s">
-        <v>157</v>
+        <v>214</v>
       </c>
       <c r="C208" s="14" t="s">
         <v>78</v>
       </c>
       <c r="D208" s="54"/>
       <c r="E208" s="14" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="F208" s="23">
         <v>1</v>
       </c>
       <c r="G208" s="9" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="H208" s="14"/>
       <c r="I208" s="33">
@@ -7412,23 +7449,23 @@
     </row>
     <row r="209" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A209" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B209" s="9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C209" s="14" t="s">
         <v>78</v>
       </c>
       <c r="D209" s="54"/>
       <c r="E209" s="14" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F209" s="23">
         <v>1</v>
       </c>
       <c r="G209" s="9" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="H209" s="14"/>
       <c r="I209" s="33">
@@ -7440,23 +7477,23 @@
     </row>
     <row r="210" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A210" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B210" s="9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C210" s="14" t="s">
         <v>78</v>
       </c>
       <c r="D210" s="54"/>
       <c r="E210" s="14" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F210" s="23">
         <v>1</v>
       </c>
       <c r="G210" s="9" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="H210" s="14"/>
       <c r="I210" s="33">
@@ -7468,23 +7505,23 @@
     </row>
     <row r="211" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A211" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B211" s="9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C211" s="14" t="s">
         <v>78</v>
       </c>
       <c r="D211" s="54"/>
       <c r="E211" s="14" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F211" s="23">
         <v>1</v>
       </c>
       <c r="G211" s="9" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="H211" s="14"/>
       <c r="I211" s="33">
@@ -7499,20 +7536,20 @@
         <v>53</v>
       </c>
       <c r="B212" s="9" t="s">
-        <v>157</v>
+        <v>214</v>
       </c>
       <c r="C212" s="14" t="s">
         <v>78</v>
       </c>
       <c r="D212" s="54"/>
       <c r="E212" s="14" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F212" s="23">
         <v>1</v>
       </c>
       <c r="G212" s="9" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="H212" s="14"/>
       <c r="I212" s="33">
@@ -7524,30 +7561,30 @@
     </row>
     <row r="213" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A213" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B213" s="9" t="s">
-        <v>157</v>
+        <v>214</v>
       </c>
       <c r="C213" s="14" t="s">
         <v>78</v>
       </c>
       <c r="D213" s="54"/>
       <c r="E213" s="14" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F213" s="23">
         <v>1</v>
       </c>
       <c r="G213" s="32" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H213" s="14"/>
       <c r="I213" s="33">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J213" s="44">
-        <v>120</v>
+        <v>30</v>
       </c>
     </row>
     <row r="214" spans="1:10" x14ac:dyDescent="0.3">
@@ -7555,20 +7592,20 @@
         <v>45</v>
       </c>
       <c r="B214" s="9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C214" s="14" t="s">
         <v>78</v>
       </c>
       <c r="D214" s="54"/>
       <c r="E214" s="14" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F214" s="23">
         <v>1</v>
       </c>
       <c r="G214" s="32" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H214" s="14"/>
       <c r="I214" s="33">
@@ -7580,23 +7617,23 @@
     </row>
     <row r="215" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A215" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B215" s="9" t="s">
-        <v>157</v>
+        <v>214</v>
       </c>
       <c r="C215" s="14" t="s">
         <v>78</v>
       </c>
       <c r="D215" s="54"/>
       <c r="E215" s="14" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="F215" s="23">
         <v>1</v>
       </c>
       <c r="G215" s="32" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H215" s="14"/>
       <c r="I215" s="33">
@@ -7608,23 +7645,23 @@
     </row>
     <row r="216" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A216" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B216" s="9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C216" s="14" t="s">
         <v>78</v>
       </c>
       <c r="D216" s="54"/>
       <c r="E216" s="14" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F216" s="19">
         <v>0.6</v>
       </c>
       <c r="G216" s="32" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H216" s="14"/>
       <c r="I216" s="33">
@@ -7636,23 +7673,23 @@
     </row>
     <row r="217" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A217" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B217" s="9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C217" s="14" t="s">
         <v>78</v>
       </c>
       <c r="D217" s="54"/>
       <c r="E217" s="14" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F217" s="19">
         <v>0.4</v>
       </c>
       <c r="G217" s="32" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H217" s="14"/>
       <c r="I217" s="33">
@@ -7664,26 +7701,26 @@
     </row>
     <row r="218" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A218" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B218" s="9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C218" s="14" t="s">
         <v>78</v>
       </c>
       <c r="D218" s="54"/>
       <c r="E218" s="14" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F218" s="23">
         <v>0.4</v>
       </c>
       <c r="G218" s="32" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H218" s="14" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="I218" s="33">
         <v>9.6000000000000002E-2</v>
@@ -7694,26 +7731,26 @@
     </row>
     <row r="219" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A219" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B219" s="10" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C219" s="14" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D219" s="54"/>
       <c r="E219" s="9" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F219" s="23">
         <v>1</v>
       </c>
       <c r="G219" s="9" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="H219" s="14" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="I219" s="33">
         <v>5.0499999999999996E-2</v>
@@ -7724,26 +7761,26 @@
     </row>
     <row r="220" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A220" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B220" s="9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C220" s="14" t="s">
         <v>78</v>
       </c>
       <c r="D220" s="54"/>
       <c r="E220" s="14" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F220" s="23">
         <v>0.6</v>
       </c>
       <c r="G220" s="32" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H220" s="14" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="I220" s="33">
         <v>9.6000000000000002E-2</v>
@@ -7754,23 +7791,23 @@
     </row>
     <row r="221" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A221" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B221" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="C221" s="14" t="s">
         <v>104</v>
-      </c>
-      <c r="B221" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="C221" s="14" t="s">
-        <v>105</v>
       </c>
       <c r="D221" s="54"/>
       <c r="E221" s="14" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F221" s="23">
         <v>1</v>
       </c>
       <c r="G221" s="14" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="H221" s="14"/>
       <c r="I221" s="33">
@@ -7782,23 +7819,23 @@
     </row>
     <row r="222" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A222" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B222" s="9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C222" s="14" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D222" s="54"/>
       <c r="E222" s="14" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F222" s="23">
         <v>1</v>
       </c>
       <c r="G222" s="14" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="H222" s="14"/>
       <c r="I222" s="33">
@@ -7810,23 +7847,23 @@
     </row>
     <row r="223" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A223" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B223" s="9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C223" s="14" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D223" s="54"/>
       <c r="E223" s="14" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F223" s="23">
         <v>1</v>
       </c>
       <c r="G223" s="14" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="H223" s="14"/>
       <c r="I223" s="33">
@@ -7838,28 +7875,28 @@
     </row>
     <row r="224" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A224" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B224" s="9" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C224" s="14" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D224" s="54" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E224" s="14" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F224" s="23">
         <v>1</v>
       </c>
       <c r="G224" s="9" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="H224" s="14" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="I224" s="33">
         <v>0.05</v>
@@ -7870,26 +7907,26 @@
     </row>
     <row r="225" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A225" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B225" s="9" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C225" s="14" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D225" s="54"/>
       <c r="E225" s="14" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F225" s="23">
         <v>1</v>
       </c>
       <c r="G225" s="9" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="H225" s="14" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="I225" s="33">
         <v>5.0499999999999996E-2</v>
@@ -7900,25 +7937,25 @@
     </row>
     <row r="226" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A226" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B226" s="9" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C226" s="14" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D226" s="54" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E226" s="14" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F226" s="23">
         <v>1</v>
       </c>
       <c r="G226" s="32" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="H226" s="14"/>
       <c r="I226" s="33">
@@ -7930,25 +7967,25 @@
     </row>
     <row r="227" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A227" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B227" s="9" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C227" s="14" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D227" s="54" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E227" s="14" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F227" s="23">
         <v>1</v>
       </c>
       <c r="G227" s="9" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="H227" s="14"/>
       <c r="I227" s="52">
@@ -7960,25 +7997,25 @@
     </row>
     <row r="228" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A228" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B228" s="9" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C228" s="14" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D228" s="54" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E228" s="14" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F228" s="23">
         <v>1</v>
       </c>
       <c r="G228" s="32" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="H228" s="14"/>
       <c r="I228" s="53">
@@ -7990,26 +8027,26 @@
     </row>
     <row r="229" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A229" s="5" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B229" s="9" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C229" s="14" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D229" s="54"/>
       <c r="E229" s="14" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F229" s="20">
         <v>1</v>
       </c>
       <c r="G229" s="9" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="H229" s="14" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="I229" s="33">
         <v>3.3333333333333333E-2</v>
@@ -8020,28 +8057,28 @@
     </row>
     <row r="230" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A230" s="2" t="s">
-        <v>80</v>
+        <v>217</v>
       </c>
       <c r="B230" s="9" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C230" s="14" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D230" s="54" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E230" s="14" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F230" s="23">
         <v>1</v>
       </c>
       <c r="G230" s="9" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="H230" s="14" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="I230" s="46">
         <v>0.10483333333333333</v>
@@ -8052,25 +8089,25 @@
     </row>
     <row r="231" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A231" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B231" s="9" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C231" s="14" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D231" s="54" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E231" s="14" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F231" s="28">
         <v>1</v>
       </c>
       <c r="G231" s="9" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="H231" s="14"/>
       <c r="I231" s="33">
@@ -8082,22 +8119,22 @@
     </row>
     <row r="232" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A232" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B232" s="9" t="s">
-        <v>157</v>
+        <v>214</v>
       </c>
       <c r="C232" s="14" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E232" s="14" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="F232" s="28">
         <v>1</v>
       </c>
       <c r="G232" s="9" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="H232" s="14"/>
       <c r="I232" s="33">
